--- a/output/full_scan/batch_seq1_2026-09-11.xlsx
+++ b/output/full_scan/batch_seq1_2026-09-11.xlsx
@@ -4884,7 +4884,7 @@
         <v/>
       </c>
       <c r="D84" s="2" t="n">
-        <v>245.0242668039078</v>
+        <v>245.0242668039077</v>
       </c>
       <c r="E84" s="2" t="n">
         <v>0</v>
